--- a/public/data/RR_shocks.xlsx
+++ b/public/data/RR_shocks.xlsx
@@ -8,34 +8,46 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/markeljanblaceri/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC53782-B49F-9D40-B47C-D150FDC73465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D1BDCD-E17B-E24E-AEA0-4E150A2DCE7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meetings" sheetId="1" r:id="rId1"/>
+    <sheet name="monthly" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>fomc</t>
   </si>
   <si>
-    <t>rr_fixed</t>
+    <t>month</t>
+  </si>
+  <si>
+    <t>rr_monthly</t>
+  </si>
+  <si>
+    <t>rr_meetings</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -65,9 +77,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -413,8 +426,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -4078,6 +4091,5004 @@
         <v>44181</v>
       </c>
       <c r="B459">
+        <v>-0.39679045397726492</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B623"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>25263</v>
+      </c>
+      <c r="B2">
+        <v>-0.19092444798281138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>25294</v>
+      </c>
+      <c r="B3">
+        <v>0.56303283871610543</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>25324</v>
+      </c>
+      <c r="B4">
+        <v>0.24622646940513007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>25355</v>
+      </c>
+      <c r="B5">
+        <v>2.5732725471031056E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>25385</v>
+      </c>
+      <c r="B6">
+        <v>0.21711864312588275</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>25416</v>
+      </c>
+      <c r="B7">
+        <v>0.33021036006553017</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>25447</v>
+      </c>
+      <c r="B8">
+        <v>4.6296088211591049E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>25477</v>
+      </c>
+      <c r="B9">
+        <v>0.17274159941019984</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>25508</v>
+      </c>
+      <c r="B10">
+        <v>5.9025758867261004E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>25538</v>
+      </c>
+      <c r="B11">
+        <v>8.9996886270981985E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>25569</v>
+      </c>
+      <c r="B12">
+        <v>-7.983079239892546E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>25600</v>
+      </c>
+      <c r="B13">
+        <v>-0.35139411081168481</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>25628</v>
+      </c>
+      <c r="B14">
+        <v>-5.8777220838764854E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>25659</v>
+      </c>
+      <c r="B15">
+        <v>-0.14452074138054669</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>25689</v>
+      </c>
+      <c r="B16">
+        <v>0.31414215993369843</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>25720</v>
+      </c>
+      <c r="B17">
+        <v>-0.13795023414688606</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>25750</v>
+      </c>
+      <c r="B18">
+        <v>-0.20088987145110648</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>25781</v>
+      </c>
+      <c r="B19">
+        <v>-0.43045393263192111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>25812</v>
+      </c>
+      <c r="B20">
+        <v>-0.21755942550859791</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>25842</v>
+      </c>
+      <c r="B21">
+        <v>-6.5936952227776083E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>25873</v>
+      </c>
+      <c r="B22">
+        <v>-0.42609916984645224</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>25903</v>
+      </c>
+      <c r="B23">
+        <v>-0.25662709854301829</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>25934</v>
+      </c>
+      <c r="B24">
+        <v>-0.65599424986343657</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>25965</v>
+      </c>
+      <c r="B25">
+        <v>-0.16398409271014178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>25993</v>
+      </c>
+      <c r="B26">
+        <v>-7.684717205195285E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>26024</v>
+      </c>
+      <c r="B27">
+        <v>0.47404390846976652</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>26054</v>
+      </c>
+      <c r="B28">
+        <v>5.9600936876369942E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>26085</v>
+      </c>
+      <c r="B29">
+        <v>0.34788122675427413</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>26115</v>
+      </c>
+      <c r="B30">
+        <v>-6.8639833572511605E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>26146</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>26177</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>26207</v>
+      </c>
+      <c r="B33">
+        <v>-0.3034240102525978</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>26238</v>
+      </c>
+      <c r="B34">
+        <v>-0.29347595385659864</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>26268</v>
+      </c>
+      <c r="B35">
+        <v>-0.86457444176962217</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>26299</v>
+      </c>
+      <c r="B36">
+        <v>-0.31723058433709395</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>26330</v>
+      </c>
+      <c r="B37">
+        <v>-0.12085272521414307</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>26359</v>
+      </c>
+      <c r="B38">
+        <v>0.2253433900183397</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>26390</v>
+      </c>
+      <c r="B39">
+        <v>-0.12455524130986734</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>26420</v>
+      </c>
+      <c r="B40">
+        <v>-6.3836928403548487E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>26451</v>
+      </c>
+      <c r="B41">
+        <v>-6.7795027752113712E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>26481</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>26512</v>
+      </c>
+      <c r="B43">
+        <v>-5.1554685831937258E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>26543</v>
+      </c>
+      <c r="B44">
+        <v>1.6718320198184922E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>26573</v>
+      </c>
+      <c r="B45">
+        <v>-5.1368669050695509E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>26604</v>
+      </c>
+      <c r="B46">
+        <v>2.1784359847753884E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>26634</v>
+      </c>
+      <c r="B47">
+        <v>4.1330506627100139E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>26665</v>
+      </c>
+      <c r="B48">
+        <v>0.33550472226634109</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>26696</v>
+      </c>
+      <c r="B49">
+        <v>0.20363813841720438</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>26724</v>
+      </c>
+      <c r="B50">
+        <v>3.615913867241527E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>26755</v>
+      </c>
+      <c r="B51">
+        <v>-3.5878323007450585E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>26785</v>
+      </c>
+      <c r="B52">
+        <v>0.33706562289790393</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>26816</v>
+      </c>
+      <c r="B53">
+        <v>0.38881270299515902</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>26846</v>
+      </c>
+      <c r="B54">
+        <v>0.1842669775376658</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>26877</v>
+      </c>
+      <c r="B55">
+        <v>0.26946172684875186</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>26908</v>
+      </c>
+      <c r="B56">
+        <v>-0.52687431852415501</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>26938</v>
+      </c>
+      <c r="B57">
+        <v>-0.79983613168046075</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>26969</v>
+      </c>
+      <c r="B58">
+        <v>-5.9737281031762048E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>26999</v>
+      </c>
+      <c r="B59">
+        <v>-0.22484152623583731</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>27030</v>
+      </c>
+      <c r="B60">
+        <v>-0.23856289773524061</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>27061</v>
+      </c>
+      <c r="B61">
+        <v>0.177211746248986</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>27089</v>
+      </c>
+      <c r="B62">
+        <v>0.80024222254532007</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>27120</v>
+      </c>
+      <c r="B63">
+        <v>0.42879549021070296</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>27150</v>
+      </c>
+      <c r="B64">
+        <v>0.38188081559475351</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>27181</v>
+      </c>
+      <c r="B65">
+        <v>0.30353300022097784</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>27211</v>
+      </c>
+      <c r="B66">
+        <v>-0.15184604254382783</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>27242</v>
+      </c>
+      <c r="B67">
+        <v>-6.7538200355658717E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>27273</v>
+      </c>
+      <c r="B68">
+        <v>-0.42653667106973414</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>27303</v>
+      </c>
+      <c r="B69">
+        <v>-0.40687095219630753</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>27334</v>
+      </c>
+      <c r="B70">
+        <v>0.14868557061759263</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>27364</v>
+      </c>
+      <c r="B71">
+        <v>-0.28892929585489457</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>27395</v>
+      </c>
+      <c r="B72">
+        <v>-0.38770894845732906</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>27426</v>
+      </c>
+      <c r="B73">
+        <v>0.20698660558690296</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>27454</v>
+      </c>
+      <c r="B74">
+        <v>-0.48604707290095828</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>27485</v>
+      </c>
+      <c r="B75">
+        <v>-0.59050623154718029</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>27515</v>
+      </c>
+      <c r="B76">
+        <v>0.1060119562384578</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>27546</v>
+      </c>
+      <c r="B77">
+        <v>0.1619143704532332</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>27576</v>
+      </c>
+      <c r="B78">
+        <v>-1.2061206945108788E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>27607</v>
+      </c>
+      <c r="B79">
+        <v>-0.18711896146437976</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>27638</v>
+      </c>
+      <c r="B80">
+        <v>-5.7504168140208423E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>27668</v>
+      </c>
+      <c r="B81">
+        <v>-0.25053340234291144</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>27699</v>
+      </c>
+      <c r="B82">
+        <v>-0.34165142203100624</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>27729</v>
+      </c>
+      <c r="B83">
+        <v>0.13882125176638663</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>27760</v>
+      </c>
+      <c r="B84">
+        <v>-0.10739809906842361</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>27791</v>
+      </c>
+      <c r="B85">
+        <v>-0.44456436643929065</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>27820</v>
+      </c>
+      <c r="B86">
+        <v>-0.23467939233618645</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
+        <v>27851</v>
+      </c>
+      <c r="B87">
+        <v>6.9494689663834042E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
+        <v>27881</v>
+      </c>
+      <c r="B88">
+        <v>-0.19678283033542232</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
+        <v>27912</v>
+      </c>
+      <c r="B89">
+        <v>-2.762384474875559E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
+        <v>27942</v>
+      </c>
+      <c r="B90">
+        <v>-0.15555841132508924</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
+        <v>27973</v>
+      </c>
+      <c r="B91">
+        <v>-9.0483373366983658E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
+        <v>28004</v>
+      </c>
+      <c r="B92">
+        <v>-1.5497796194317159E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
+        <v>28034</v>
+      </c>
+      <c r="B93">
+        <v>-0.13224018109213578</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
+        <v>28065</v>
+      </c>
+      <c r="B94">
+        <v>-5.1223006966875678E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
+        <v>28095</v>
+      </c>
+      <c r="B95">
+        <v>-0.1418772165697626</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
+        <v>28126</v>
+      </c>
+      <c r="B96">
+        <v>-0.16658515306584698</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
+        <v>28157</v>
+      </c>
+      <c r="B97">
+        <v>-0.15038352210102648</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
+        <v>28185</v>
+      </c>
+      <c r="B98">
+        <v>-0.24347576547694008</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
+        <v>28216</v>
+      </c>
+      <c r="B99">
+        <v>0.12084490054475155</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
+        <v>28246</v>
+      </c>
+      <c r="B100">
+        <v>-0.23706708093935908</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
+        <v>28277</v>
+      </c>
+      <c r="B101">
+        <v>-0.18801684539288263</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
+        <v>28307</v>
+      </c>
+      <c r="B102">
+        <v>-0.25333749136534583</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" s="1">
+        <v>28338</v>
+      </c>
+      <c r="B103">
+        <v>-7.3339010607081367E-3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" s="1">
+        <v>28369</v>
+      </c>
+      <c r="B104">
+        <v>6.706771442476156E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" s="1">
+        <v>28399</v>
+      </c>
+      <c r="B105">
+        <v>-5.4771308101922309E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" s="1">
+        <v>28430</v>
+      </c>
+      <c r="B106">
+        <v>-7.8766367587333783E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" s="1">
+        <v>28460</v>
+      </c>
+      <c r="B107">
+        <v>-0.11150743574621168</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" s="1">
+        <v>28491</v>
+      </c>
+      <c r="B108">
+        <v>-0.20532518762335222</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" s="1">
+        <v>28522</v>
+      </c>
+      <c r="B109">
+        <v>1.6498083992431242E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" s="1">
+        <v>28550</v>
+      </c>
+      <c r="B110">
+        <v>-1.2524954737946162E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" s="1">
+        <v>28581</v>
+      </c>
+      <c r="B111">
+        <v>-7.9873222102705921E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" s="1">
+        <v>28611</v>
+      </c>
+      <c r="B112">
+        <v>-0.20169749180930957</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" s="1">
+        <v>28642</v>
+      </c>
+      <c r="B113">
+        <v>0.15859583794079996</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" s="1">
+        <v>28672</v>
+      </c>
+      <c r="B114">
+        <v>-0.11922968920816163</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" s="1">
+        <v>28703</v>
+      </c>
+      <c r="B115">
+        <v>-7.1466952703488573E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" s="1">
+        <v>28734</v>
+      </c>
+      <c r="B116">
+        <v>-0.10173185913394095</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117" s="1">
+        <v>28764</v>
+      </c>
+      <c r="B117">
+        <v>0.15340432012349914</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118" s="1">
+        <v>28795</v>
+      </c>
+      <c r="B118">
+        <v>0.16379212872290055</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119" s="1">
+        <v>28825</v>
+      </c>
+      <c r="B119">
+        <v>-2.5342065219199961E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120" s="1">
+        <v>28856</v>
+      </c>
+      <c r="B120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121" s="1">
+        <v>28887</v>
+      </c>
+      <c r="B121">
+        <v>-0.15416014676043227</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122" s="1">
+        <v>28915</v>
+      </c>
+      <c r="B122">
+        <v>8.5864444306046617E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123" s="1">
+        <v>28946</v>
+      </c>
+      <c r="B123">
+        <v>-7.1285407211748128E-2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124" s="1">
+        <v>28976</v>
+      </c>
+      <c r="B124">
+        <v>5.6098518165497997E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125" s="1">
+        <v>29007</v>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126" s="1">
+        <v>29037</v>
+      </c>
+      <c r="B126">
+        <v>0.65727808252012621</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127" s="1">
+        <v>29068</v>
+      </c>
+      <c r="B127">
+        <v>0.34841355907308325</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>29099</v>
+      </c>
+      <c r="B128">
+        <v>-7.2825664816739522E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>29129</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>29160</v>
+      </c>
+      <c r="B130">
+        <v>0.28882516401567782</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>29190</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>29221</v>
+      </c>
+      <c r="B132">
+        <v>0.14136961056964928</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>29252</v>
+      </c>
+      <c r="B133">
+        <v>0.2642778417482633</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>29281</v>
+      </c>
+      <c r="B134">
+        <v>1.4881401517010957</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>29312</v>
+      </c>
+      <c r="B135">
+        <v>-3.3037788406733761</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>29342</v>
+      </c>
+      <c r="B136">
+        <v>-0.84150706258578167</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>29373</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>29403</v>
+      </c>
+      <c r="B138">
+        <v>0.39225734937953155</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>29434</v>
+      </c>
+      <c r="B139">
+        <v>-4.1675067169520019E-2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>29465</v>
+      </c>
+      <c r="B140">
+        <v>0.83856342124580774</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>29495</v>
+      </c>
+      <c r="B141">
+        <v>1.342346963246108</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>29526</v>
+      </c>
+      <c r="B142">
+        <v>1.8418580215760358</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>29556</v>
+      </c>
+      <c r="B143">
+        <v>-0.68916771097245288</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>29587</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>29618</v>
+      </c>
+      <c r="B145">
+        <v>-0.73120355461757824</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>29646</v>
+      </c>
+      <c r="B146">
+        <v>0.38763926660023307</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>29677</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
+        <v>29707</v>
+      </c>
+      <c r="B148">
+        <v>1.605231211114996</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149" s="1">
+        <v>29738</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150" s="1">
+        <v>29768</v>
+      </c>
+      <c r="B150">
+        <v>-0.6268250076114894</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151" s="1">
+        <v>29799</v>
+      </c>
+      <c r="B151">
+        <v>-9.7212075354426775E-2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152" s="1">
+        <v>29830</v>
+      </c>
+      <c r="B152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153" s="1">
+        <v>29860</v>
+      </c>
+      <c r="B153">
+        <v>-0.52930558890601165</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154" s="1">
+        <v>29891</v>
+      </c>
+      <c r="B154">
+        <v>-0.4091116740746521</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155" s="1">
+        <v>29921</v>
+      </c>
+      <c r="B155">
+        <v>0.10854704234084733</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156" s="1">
+        <v>29952</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157" s="1">
+        <v>29983</v>
+      </c>
+      <c r="B157">
+        <v>0.98290714202080909</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158" s="1">
+        <v>30011</v>
+      </c>
+      <c r="B158">
+        <v>-0.36177303045958464</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159" s="1">
+        <v>30042</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160" s="1">
+        <v>30072</v>
+      </c>
+      <c r="B160">
+        <v>-0.1467479648106127</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161" s="1">
+        <v>30103</v>
+      </c>
+      <c r="B161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162" s="1">
+        <v>30133</v>
+      </c>
+      <c r="B162">
+        <v>-0.20162299445287479</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163" s="1">
+        <v>30164</v>
+      </c>
+      <c r="B163">
+        <v>-0.31645037470617554</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164" s="1">
+        <v>30195</v>
+      </c>
+      <c r="B164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165" s="1">
+        <v>30225</v>
+      </c>
+      <c r="B165">
+        <v>-0.33826412910759068</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166" s="1">
+        <v>30256</v>
+      </c>
+      <c r="B166">
+        <v>-4.6132549425119518E-2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167" s="1">
+        <v>30286</v>
+      </c>
+      <c r="B167">
+        <v>0.48069698889868789</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168" s="1">
+        <v>30317</v>
+      </c>
+      <c r="B168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169" s="1">
+        <v>30348</v>
+      </c>
+      <c r="B169">
+        <v>8.0885165043109816E-2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A170" s="1">
+        <v>30376</v>
+      </c>
+      <c r="B170">
+        <v>0.10006384109942615</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A171" s="1">
+        <v>30407</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A172" s="1">
+        <v>30437</v>
+      </c>
+      <c r="B172">
+        <v>7.0448216534498009E-3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A173" s="1">
+        <v>30468</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A174" s="1">
+        <v>30498</v>
+      </c>
+      <c r="B174">
+        <v>3.8165604473917314E-2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A175" s="1">
+        <v>30529</v>
+      </c>
+      <c r="B175">
+        <v>-0.22253599392745751</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A176" s="1">
+        <v>30560</v>
+      </c>
+      <c r="B176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A177" s="1">
+        <v>30590</v>
+      </c>
+      <c r="B177">
+        <v>0.16646555279813577</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A178" s="1">
+        <v>30621</v>
+      </c>
+      <c r="B178">
+        <v>-0.17982155764550187</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A179" s="1">
+        <v>30651</v>
+      </c>
+      <c r="B179">
+        <v>0.14356727775917288</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A180" s="1">
+        <v>30682</v>
+      </c>
+      <c r="B180">
+        <v>0.13748508025819409</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A181" s="1">
+        <v>30713</v>
+      </c>
+      <c r="B181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A182" s="1">
+        <v>30742</v>
+      </c>
+      <c r="B182">
+        <v>-5.8106315384347962E-2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A183" s="1">
+        <v>30773</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A184" s="1">
+        <v>30803</v>
+      </c>
+      <c r="B184">
+        <v>8.0312413865735635E-2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A185" s="1">
+        <v>30834</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A186" s="1">
+        <v>30864</v>
+      </c>
+      <c r="B186">
+        <v>0.36065333113554682</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A187" s="1">
+        <v>30895</v>
+      </c>
+      <c r="B187">
+        <v>-3.2398825603263598E-2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A188" s="1">
+        <v>30926</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A189" s="1">
+        <v>30956</v>
+      </c>
+      <c r="B189">
+        <v>-4.9569890686253504E-2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A190" s="1">
+        <v>30987</v>
+      </c>
+      <c r="B190">
+        <v>-0.56302393839974418</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A191" s="1">
+        <v>31017</v>
+      </c>
+      <c r="B191">
+        <v>-0.22457645426522244</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A192" s="1">
+        <v>31048</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A193" s="1">
+        <v>31079</v>
+      </c>
+      <c r="B193">
+        <v>-0.10482101084045248</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A194" s="1">
+        <v>31107</v>
+      </c>
+      <c r="B194">
+        <v>0.16846041823382593</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A195" s="1">
+        <v>31138</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A196" s="1">
+        <v>31168</v>
+      </c>
+      <c r="B196">
+        <v>-0.20156646223526833</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A197" s="1">
+        <v>31199</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A198" s="1">
+        <v>31229</v>
+      </c>
+      <c r="B198">
+        <v>5.3439679592392819E-2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A199" s="1">
+        <v>31260</v>
+      </c>
+      <c r="B199">
+        <v>0.14737847500277659</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A200" s="1">
+        <v>31291</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A201" s="1">
+        <v>31321</v>
+      </c>
+      <c r="B201">
+        <v>7.725115182945802E-2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A202" s="1">
+        <v>31352</v>
+      </c>
+      <c r="B202">
+        <v>-1.1946990738382429E-2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A203" s="1">
+        <v>31382</v>
+      </c>
+      <c r="B203">
+        <v>-9.6354332430660911E-2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A204" s="1">
+        <v>31413</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A205" s="1">
+        <v>31444</v>
+      </c>
+      <c r="B205">
+        <v>-8.3399602296623868E-2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A206" s="1">
+        <v>31472</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A207" s="1">
+        <v>31503</v>
+      </c>
+      <c r="B207">
+        <v>0.18499516641608277</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A208" s="1">
+        <v>31533</v>
+      </c>
+      <c r="B208">
+        <v>9.3344990379693502E-2</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A209" s="1">
+        <v>31564</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A210" s="1">
+        <v>31594</v>
+      </c>
+      <c r="B210">
+        <v>-0.22142174879097443</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A211" s="1">
+        <v>31625</v>
+      </c>
+      <c r="B211">
+        <v>-0.27392136013632584</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A212" s="1">
+        <v>31656</v>
+      </c>
+      <c r="B212">
+        <v>6.8496045440292344E-3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A213" s="1">
+        <v>31686</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A214" s="1">
+        <v>31717</v>
+      </c>
+      <c r="B214">
+        <v>4.7178206723866904E-2</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A215" s="1">
+        <v>31747</v>
+      </c>
+      <c r="B215">
+        <v>-3.9235232886382816E-2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A216" s="1">
+        <v>31778</v>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A217" s="1">
+        <v>31809</v>
+      </c>
+      <c r="B217">
+        <v>0.16073071800393066</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A218" s="1">
+        <v>31837</v>
+      </c>
+      <c r="B218">
+        <v>0.20528436684193532</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A219" s="1">
+        <v>31868</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A220" s="1">
+        <v>31898</v>
+      </c>
+      <c r="B220">
+        <v>0.26222712429650968</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A221" s="1">
+        <v>31929</v>
+      </c>
+      <c r="B221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A222" s="1">
+        <v>31959</v>
+      </c>
+      <c r="B222">
+        <v>-1.7906860976333015E-2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A223" s="1">
+        <v>31990</v>
+      </c>
+      <c r="B223">
+        <v>-9.1305799194066149E-3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A224" s="1">
+        <v>32021</v>
+      </c>
+      <c r="B224">
+        <v>-9.4777038550213674E-2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A225" s="1">
+        <v>32051</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A226" s="1">
+        <v>32082</v>
+      </c>
+      <c r="B226">
+        <v>-7.5157822242229083E-2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A227" s="1">
+        <v>32112</v>
+      </c>
+      <c r="B227">
+        <v>-0.11217308260309185</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A228" s="1">
+        <v>32143</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A229" s="1">
+        <v>32174</v>
+      </c>
+      <c r="B229">
+        <v>-0.15266630810538429</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A230" s="1">
+        <v>32203</v>
+      </c>
+      <c r="B230">
+        <v>8.844723836794488E-2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A231" s="1">
+        <v>32234</v>
+      </c>
+      <c r="B231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A232" s="1">
+        <v>32264</v>
+      </c>
+      <c r="B232">
+        <v>0.21604103948119138</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A233" s="1">
+        <v>32295</v>
+      </c>
+      <c r="B233">
+        <v>0.3389211706894501</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A234" s="1">
+        <v>32325</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A235" s="1">
+        <v>32356</v>
+      </c>
+      <c r="B235">
+        <v>-6.5088992614364613E-2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A236" s="1">
+        <v>32387</v>
+      </c>
+      <c r="B236">
+        <v>1.2192441862691705E-2</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A237" s="1">
+        <v>32417</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A238" s="1">
+        <v>32448</v>
+      </c>
+      <c r="B238">
+        <v>-1.3523339402639121E-2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A239" s="1">
+        <v>32478</v>
+      </c>
+      <c r="B239">
+        <v>0.47730162733512033</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A240" s="1">
+        <v>32509</v>
+      </c>
+      <c r="B240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A241" s="1">
+        <v>32540</v>
+      </c>
+      <c r="B241">
+        <v>0.26544101019577254</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A242" s="1">
+        <v>32568</v>
+      </c>
+      <c r="B242">
+        <v>9.6713975503018149E-2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A243" s="1">
+        <v>32599</v>
+      </c>
+      <c r="B243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A244" s="1">
+        <v>32629</v>
+      </c>
+      <c r="B244">
+        <v>0.14318412463673161</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A245" s="1">
+        <v>32660</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A246" s="1">
+        <v>32690</v>
+      </c>
+      <c r="B246">
+        <v>1.4277344604384568E-2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A247" s="1">
+        <v>32721</v>
+      </c>
+      <c r="B247">
+        <v>-7.3203581775186641E-2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A248" s="1">
+        <v>32752</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A249" s="1">
+        <v>32782</v>
+      </c>
+      <c r="B249">
+        <v>-1.9074656500305917E-2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A250" s="1">
+        <v>32813</v>
+      </c>
+      <c r="B250">
+        <v>0.1214528266730925</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A251" s="1">
+        <v>32843</v>
+      </c>
+      <c r="B251">
+        <v>-5.9347834408963296E-2</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A252" s="1">
+        <v>32874</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A253" s="1">
+        <v>32905</v>
+      </c>
+      <c r="B253">
+        <v>0.23748489654576668</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A254" s="1">
+        <v>32933</v>
+      </c>
+      <c r="B254">
+        <v>-6.0477053200712651E-2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A255" s="1">
+        <v>32964</v>
+      </c>
+      <c r="B255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A256" s="1">
+        <v>32994</v>
+      </c>
+      <c r="B256">
+        <v>3.0179210242245392E-2</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A257" s="1">
+        <v>33025</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A258" s="1">
+        <v>33055</v>
+      </c>
+      <c r="B258">
+        <v>-9.4079757877573417E-2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A259" s="1">
+        <v>33086</v>
+      </c>
+      <c r="B259">
+        <v>0.16286057849826696</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A260" s="1">
+        <v>33117</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A261" s="1">
+        <v>33147</v>
+      </c>
+      <c r="B261">
+        <v>-9.6063109870728192E-2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A262" s="1">
+        <v>33178</v>
+      </c>
+      <c r="B262">
+        <v>1.0538800459626907E-2</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A263" s="1">
+        <v>33208</v>
+      </c>
+      <c r="B263">
+        <v>-7.9336042871107737E-2</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A264" s="1">
+        <v>33239</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A265" s="1">
+        <v>33270</v>
+      </c>
+      <c r="B265">
+        <v>-0.21383689336251682</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A266" s="1">
+        <v>33298</v>
+      </c>
+      <c r="B266">
+        <v>0.27147674198004629</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A267" s="1">
+        <v>33329</v>
+      </c>
+      <c r="B267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A268" s="1">
+        <v>33359</v>
+      </c>
+      <c r="B268">
+        <v>0.22284573929325524</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A269" s="1">
+        <v>33390</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A270" s="1">
+        <v>33420</v>
+      </c>
+      <c r="B270">
+        <v>-5.7683388758791074E-2</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A271" s="1">
+        <v>33451</v>
+      </c>
+      <c r="B271">
+        <v>0.17374039163410712</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A272" s="1">
+        <v>33482</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A273" s="1">
+        <v>33512</v>
+      </c>
+      <c r="B273">
+        <v>-1.0838519528370656E-2</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A274" s="1">
+        <v>33543</v>
+      </c>
+      <c r="B274">
+        <v>-0.14125959113932357</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A275" s="1">
+        <v>33573</v>
+      </c>
+      <c r="B275">
+        <v>0.11618029255370033</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A276" s="1">
+        <v>33604</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A277" s="1">
+        <v>33635</v>
+      </c>
+      <c r="B277">
+        <v>3.9452637034103122E-2</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A278" s="1">
+        <v>33664</v>
+      </c>
+      <c r="B278">
+        <v>-9.3273025639134866E-2</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A279" s="1">
+        <v>33695</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A280" s="1">
+        <v>33725</v>
+      </c>
+      <c r="B280">
+        <v>0.11286652298750867</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A281" s="1">
+        <v>33756</v>
+      </c>
+      <c r="B281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A282" s="1">
+        <v>33786</v>
+      </c>
+      <c r="B282">
+        <v>-7.7548091694146892E-2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A283" s="1">
+        <v>33817</v>
+      </c>
+      <c r="B283">
+        <v>-2.1903942284530617E-2</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A284" s="1">
+        <v>33848</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A285" s="1">
+        <v>33878</v>
+      </c>
+      <c r="B285">
+        <v>-0.19421409723918859</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A286" s="1">
+        <v>33909</v>
+      </c>
+      <c r="B286">
+        <v>-3.5966796889714783E-2</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A287" s="1">
+        <v>33939</v>
+      </c>
+      <c r="B287">
+        <v>-0.19432645905008417</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A288" s="1">
+        <v>33970</v>
+      </c>
+      <c r="B288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A289" s="1">
+        <v>34001</v>
+      </c>
+      <c r="B289">
+        <v>4.3498854533043224E-2</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A290" s="1">
+        <v>34029</v>
+      </c>
+      <c r="B290">
+        <v>-6.2234792932136025E-2</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A291" s="1">
+        <v>34060</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A292" s="1">
+        <v>34090</v>
+      </c>
+      <c r="B292">
+        <v>0.27563618835147174</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A293" s="1">
+        <v>34121</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A294" s="1">
+        <v>34151</v>
+      </c>
+      <c r="B294">
+        <v>-3.2562099529942282E-3</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A295" s="1">
+        <v>34182</v>
+      </c>
+      <c r="B295">
+        <v>2.4774762207236914E-2</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A296" s="1">
+        <v>34213</v>
+      </c>
+      <c r="B296">
+        <v>0.10853246082186953</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A297" s="1">
+        <v>34243</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A298" s="1">
+        <v>34274</v>
+      </c>
+      <c r="B298">
+        <v>-5.2845400348046287E-2</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A299" s="1">
+        <v>34304</v>
+      </c>
+      <c r="B299">
+        <v>-0.17081043456815154</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A300" s="1">
+        <v>34335</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A301" s="1">
+        <v>34366</v>
+      </c>
+      <c r="B301">
+        <v>0.17682249390710073</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A302" s="1">
+        <v>34394</v>
+      </c>
+      <c r="B302">
+        <v>0.33830066742803755</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A303" s="1">
+        <v>34425</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A304" s="1">
+        <v>34455</v>
+      </c>
+      <c r="B304">
+        <v>0.32437867802285286</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A305" s="1">
+        <v>34486</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A306" s="1">
+        <v>34516</v>
+      </c>
+      <c r="B306">
+        <v>5.6377148108999603E-2</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A307" s="1">
+        <v>34547</v>
+      </c>
+      <c r="B307">
+        <v>0.45315999224681874</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A308" s="1">
+        <v>34578</v>
+      </c>
+      <c r="B308">
+        <v>6.5473739990082241E-2</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A309" s="1">
+        <v>34608</v>
+      </c>
+      <c r="B309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A310" s="1">
+        <v>34639</v>
+      </c>
+      <c r="B310">
+        <v>0.61996266987594217</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A311" s="1">
+        <v>34669</v>
+      </c>
+      <c r="B311">
+        <v>-0.16717510533642946</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A312" s="1">
+        <v>34700</v>
+      </c>
+      <c r="B312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A313" s="1">
+        <v>34731</v>
+      </c>
+      <c r="B313">
+        <v>0.52208259936698831</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A314" s="1">
+        <v>34759</v>
+      </c>
+      <c r="B314">
+        <v>0.21671313817264193</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A315" s="1">
+        <v>34790</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A316" s="1">
+        <v>34820</v>
+      </c>
+      <c r="B316">
+        <v>0.21589492930265627</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A317" s="1">
+        <v>34851</v>
+      </c>
+      <c r="B317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A318" s="1">
+        <v>34881</v>
+      </c>
+      <c r="B318">
+        <v>3.6228377668777512E-2</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A319" s="1">
+        <v>34912</v>
+      </c>
+      <c r="B319">
+        <v>-3.5875246770365105E-3</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A320" s="1">
+        <v>34943</v>
+      </c>
+      <c r="B320">
+        <v>7.9396426226006137E-2</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A321" s="1">
+        <v>34973</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A322" s="1">
+        <v>35004</v>
+      </c>
+      <c r="B322">
+        <v>0.11107871652928274</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A323" s="1">
+        <v>35034</v>
+      </c>
+      <c r="B323">
+        <v>-0.12896782816961289</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A324" s="1">
+        <v>35065</v>
+      </c>
+      <c r="B324">
+        <v>4.1009524625515104E-2</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A325" s="1">
+        <v>35096</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A326" s="1">
+        <v>35125</v>
+      </c>
+      <c r="B326">
+        <v>7.4340207765721559E-3</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A327" s="1">
+        <v>35156</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A328" s="1">
+        <v>35186</v>
+      </c>
+      <c r="B328">
+        <v>-1.2096260967170706E-2</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A329" s="1">
+        <v>35217</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A330" s="1">
+        <v>35247</v>
+      </c>
+      <c r="B330">
+        <v>-7.2579773861964937E-3</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A331" s="1">
+        <v>35278</v>
+      </c>
+      <c r="B331">
+        <v>-2.3597033246838744E-2</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A332" s="1">
+        <v>35309</v>
+      </c>
+      <c r="B332">
+        <v>-2.0231314660257385E-3</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A333" s="1">
+        <v>35339</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A334" s="1">
+        <v>35370</v>
+      </c>
+      <c r="B334">
+        <v>6.6682229483135E-2</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A335" s="1">
+        <v>35400</v>
+      </c>
+      <c r="B335">
+        <v>-7.1412023503325079E-3</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A336" s="1">
+        <v>35431</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A337" s="1">
+        <v>35462</v>
+      </c>
+      <c r="B337">
+        <v>3.5197333545213483E-2</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A338" s="1">
+        <v>35490</v>
+      </c>
+      <c r="B338">
+        <v>8.1678835688005602E-2</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A339" s="1">
+        <v>35521</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A340" s="1">
+        <v>35551</v>
+      </c>
+      <c r="B340">
+        <v>7.7792085767420804E-2</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A341" s="1">
+        <v>35582</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A342" s="1">
+        <v>35612</v>
+      </c>
+      <c r="B342">
+        <v>-8.4771888501704362E-2</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A343" s="1">
+        <v>35643</v>
+      </c>
+      <c r="B343">
+        <v>0.12948052416088743</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A344" s="1">
+        <v>35674</v>
+      </c>
+      <c r="B344">
+        <v>-0.12025214523806613</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A345" s="1">
+        <v>35704</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A346" s="1">
+        <v>35735</v>
+      </c>
+      <c r="B346">
+        <v>-4.3641544087245243E-2</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A347" s="1">
+        <v>35765</v>
+      </c>
+      <c r="B347">
+        <v>-6.9662382898642477E-3</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A348" s="1">
+        <v>35796</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A349" s="1">
+        <v>35827</v>
+      </c>
+      <c r="B349">
+        <v>1.7881895989156054E-2</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A350" s="1">
+        <v>35855</v>
+      </c>
+      <c r="B350">
+        <v>-1.9872419247609744E-2</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A351" s="1">
+        <v>35886</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A352" s="1">
+        <v>35916</v>
+      </c>
+      <c r="B352">
+        <v>-3.3190339654106046E-2</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A353" s="1">
+        <v>35947</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A354" s="1">
+        <v>35977</v>
+      </c>
+      <c r="B354">
+        <v>8.8237404045446527E-2</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A355" s="1">
+        <v>36008</v>
+      </c>
+      <c r="B355">
+        <v>6.4738450550137633E-2</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A356" s="1">
+        <v>36039</v>
+      </c>
+      <c r="B356">
+        <v>-0.22375836789055106</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A357" s="1">
+        <v>36069</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A358" s="1">
+        <v>36100</v>
+      </c>
+      <c r="B358">
+        <v>-0.14139764922874198</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A359" s="1">
+        <v>36130</v>
+      </c>
+      <c r="B359">
+        <v>-0.13915897149892709</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A360" s="1">
+        <v>36161</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A361" s="1">
+        <v>36192</v>
+      </c>
+      <c r="B361">
+        <v>-7.0368342888715921E-2</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A362" s="1">
+        <v>36220</v>
+      </c>
+      <c r="B362">
+        <v>-0.12831588559848281</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A363" s="1">
+        <v>36251</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A364" s="1">
+        <v>36281</v>
+      </c>
+      <c r="B364">
+        <v>-6.9168301270641858E-2</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A365" s="1">
+        <v>36312</v>
+      </c>
+      <c r="B365">
+        <v>0.24986187090303652</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A366" s="1">
+        <v>36342</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A367" s="1">
+        <v>36373</v>
+      </c>
+      <c r="B367">
+        <v>0.26692480916283684</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A368" s="1">
+        <v>36404</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A369" s="1">
+        <v>36434</v>
+      </c>
+      <c r="B369">
+        <v>-0.1238421572285392</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A370" s="1">
+        <v>36465</v>
+      </c>
+      <c r="B370">
+        <v>0.21861915334949333</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A371" s="1">
+        <v>36495</v>
+      </c>
+      <c r="B371">
+        <v>-0.21706218600175023</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A372" s="1">
+        <v>36526</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A373" s="1">
+        <v>36557</v>
+      </c>
+      <c r="B373">
+        <v>0.11757515110250663</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A374" s="1">
+        <v>36586</v>
+      </c>
+      <c r="B374">
+        <v>8.8194022586522702E-3</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A375" s="1">
+        <v>36617</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A376" s="1">
+        <v>36647</v>
+      </c>
+      <c r="B376">
+        <v>0.38159436645046418</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A377" s="1">
+        <v>36678</v>
+      </c>
+      <c r="B377">
+        <v>8.4338334458013697E-2</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A378" s="1">
+        <v>36708</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A379" s="1">
+        <v>36739</v>
+      </c>
+      <c r="B379">
+        <v>3.4779898730849607E-2</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A380" s="1">
+        <v>36770</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A381" s="1">
+        <v>36800</v>
+      </c>
+      <c r="B381">
+        <v>-4.6419602153586502E-2</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A382" s="1">
+        <v>36831</v>
+      </c>
+      <c r="B382">
+        <v>2.8653188049340014E-2</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A383" s="1">
+        <v>36861</v>
+      </c>
+      <c r="B383">
+        <v>0.24092376788838291</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A384" s="1">
+        <v>36892</v>
+      </c>
+      <c r="B384">
+        <v>1.9965117214237993E-2</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A385" s="1">
+        <v>36923</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A386" s="1">
+        <v>36951</v>
+      </c>
+      <c r="B386">
+        <v>-0.50021386215111974</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A387" s="1">
+        <v>36982</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A388" s="1">
+        <v>37012</v>
+      </c>
+      <c r="B388">
+        <v>-0.41919350510606213</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A389" s="1">
+        <v>37043</v>
+      </c>
+      <c r="B389">
+        <v>-0.16373504732006858</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A390" s="1">
+        <v>37073</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A391" s="1">
+        <v>37104</v>
+      </c>
+      <c r="B391">
+        <v>-0.11056937892369798</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A392" s="1">
+        <v>37135</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A393" s="1">
+        <v>37165</v>
+      </c>
+      <c r="B393">
+        <v>-0.11959761987300144</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A394" s="1">
+        <v>37196</v>
+      </c>
+      <c r="B394">
+        <v>-0.18510395959174897</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A395" s="1">
+        <v>37226</v>
+      </c>
+      <c r="B395">
+        <v>-0.24059135604726642</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A396" s="1">
+        <v>37257</v>
+      </c>
+      <c r="B396">
+        <v>-0.1563807886139352</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A397" s="1">
+        <v>37288</v>
+      </c>
+      <c r="B397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A398" s="1">
+        <v>37316</v>
+      </c>
+      <c r="B398">
+        <v>-0.34930332741557368</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A399" s="1">
+        <v>37347</v>
+      </c>
+      <c r="B399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A400" s="1">
+        <v>37377</v>
+      </c>
+      <c r="B400">
+        <v>0.16112241413649755</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A401" s="1">
+        <v>37408</v>
+      </c>
+      <c r="B401">
+        <v>2.9441000460626115E-3</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A402" s="1">
+        <v>37438</v>
+      </c>
+      <c r="B402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A403" s="1">
+        <v>37469</v>
+      </c>
+      <c r="B403">
+        <v>0.11700147705967788</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A404" s="1">
+        <v>37500</v>
+      </c>
+      <c r="B404">
+        <v>-6.6166639598506174E-2</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A405" s="1">
+        <v>37530</v>
+      </c>
+      <c r="B405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A406" s="1">
+        <v>37561</v>
+      </c>
+      <c r="B406">
+        <v>-0.34040878482855497</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A407" s="1">
+        <v>37591</v>
+      </c>
+      <c r="B407">
+        <v>-1.9624316923230044E-2</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A408" s="1">
+        <v>37622</v>
+      </c>
+      <c r="B408">
+        <v>-2.4473774593730187E-2</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A409" s="1">
+        <v>37653</v>
+      </c>
+      <c r="B409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A410" s="1">
+        <v>37681</v>
+      </c>
+      <c r="B410">
+        <v>-2.3825575654837978E-3</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A411" s="1">
+        <v>37712</v>
+      </c>
+      <c r="B411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A412" s="1">
+        <v>37742</v>
+      </c>
+      <c r="B412">
+        <v>-1.8443621135378327E-2</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A413" s="1">
+        <v>37773</v>
+      </c>
+      <c r="B413">
+        <v>-0.24848044525326532</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A414" s="1">
+        <v>37803</v>
+      </c>
+      <c r="B414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A415" s="1">
+        <v>37834</v>
+      </c>
+      <c r="B415">
+        <v>-0.10044244216906387</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A416" s="1">
+        <v>37865</v>
+      </c>
+      <c r="B416">
+        <v>-0.20913464628837539</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A417" s="1">
+        <v>37895</v>
+      </c>
+      <c r="B417">
+        <v>-0.16487688628841538</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A418" s="1">
+        <v>37926</v>
+      </c>
+      <c r="B418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A419" s="1">
+        <v>37956</v>
+      </c>
+      <c r="B419">
+        <v>-0.2032063745381642</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A420" s="1">
+        <v>37987</v>
+      </c>
+      <c r="B420">
+        <v>-0.10440434674427142</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A421" s="1">
+        <v>38018</v>
+      </c>
+      <c r="B421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A422" s="1">
+        <v>38047</v>
+      </c>
+      <c r="B422">
+        <v>1.4557683453984465E-2</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A423" s="1">
+        <v>38078</v>
+      </c>
+      <c r="B423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A424" s="1">
+        <v>38108</v>
+      </c>
+      <c r="B424">
+        <v>-0.13020759592164124</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A425" s="1">
+        <v>38139</v>
+      </c>
+      <c r="B425">
+        <v>0.10230154843801273</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A426" s="1">
+        <v>38169</v>
+      </c>
+      <c r="B426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A427" s="1">
+        <v>38200</v>
+      </c>
+      <c r="B427">
+        <v>0.29178001425888433</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A428" s="1">
+        <v>38231</v>
+      </c>
+      <c r="B428">
+        <v>0.17129658820895344</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A429" s="1">
+        <v>38261</v>
+      </c>
+      <c r="B429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A430" s="1">
+        <v>38292</v>
+      </c>
+      <c r="B430">
+        <v>0.27782551107792552</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A431" s="1">
+        <v>38322</v>
+      </c>
+      <c r="B431">
+        <v>0.14864289105154344</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A432" s="1">
+        <v>38353</v>
+      </c>
+      <c r="B432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A433" s="1">
+        <v>38384</v>
+      </c>
+      <c r="B433">
+        <v>0.12690634057474531</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A434" s="1">
+        <v>38412</v>
+      </c>
+      <c r="B434">
+        <v>4.0102701583106137E-2</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A435" s="1">
+        <v>38443</v>
+      </c>
+      <c r="B435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A436" s="1">
+        <v>38473</v>
+      </c>
+      <c r="B436">
+        <v>0.25934515128521851</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A437" s="1">
+        <v>38504</v>
+      </c>
+      <c r="B437">
+        <v>0.24614565165977981</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A438" s="1">
+        <v>38534</v>
+      </c>
+      <c r="B438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A439" s="1">
+        <v>38565</v>
+      </c>
+      <c r="B439">
+        <v>7.9921201706973255E-2</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A440" s="1">
+        <v>38596</v>
+      </c>
+      <c r="B440">
+        <v>0.2695349252325358</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A441" s="1">
+        <v>38626</v>
+      </c>
+      <c r="B441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A442" s="1">
+        <v>38657</v>
+      </c>
+      <c r="B442">
+        <v>0.2315858895376863</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A443" s="1">
+        <v>38687</v>
+      </c>
+      <c r="B443">
+        <v>0.13827451003889588</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A444" s="1">
+        <v>38718</v>
+      </c>
+      <c r="B444">
+        <v>0.15277761324485364</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A445" s="1">
+        <v>38749</v>
+      </c>
+      <c r="B445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A446" s="1">
+        <v>38777</v>
+      </c>
+      <c r="B446">
+        <v>0.10519563201995361</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A447" s="1">
+        <v>38808</v>
+      </c>
+      <c r="B447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A448" s="1">
+        <v>38838</v>
+      </c>
+      <c r="B448">
+        <v>0.19237404996468732</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A449" s="1">
+        <v>38869</v>
+      </c>
+      <c r="B449">
+        <v>0.40822940404724151</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A450" s="1">
+        <v>38899</v>
+      </c>
+      <c r="B450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A451" s="1">
+        <v>38930</v>
+      </c>
+      <c r="B451">
+        <v>6.7544676363062925E-2</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A452" s="1">
+        <v>38961</v>
+      </c>
+      <c r="B452">
+        <v>9.9684456595342585E-2</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A453" s="1">
+        <v>38991</v>
+      </c>
+      <c r="B453">
+        <v>-4.2888868904574863E-2</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A454" s="1">
+        <v>39022</v>
+      </c>
+      <c r="B454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A455" s="1">
+        <v>39052</v>
+      </c>
+      <c r="B455">
+        <v>9.154931722558883E-2</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A456" s="1">
+        <v>39083</v>
+      </c>
+      <c r="B456">
+        <v>-4.3185558282321269E-2</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A457" s="1">
+        <v>39114</v>
+      </c>
+      <c r="B457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A458" s="1">
+        <v>39142</v>
+      </c>
+      <c r="B458">
+        <v>0.13265268605610409</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A459" s="1">
+        <v>39173</v>
+      </c>
+      <c r="B459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A460" s="1">
+        <v>39203</v>
+      </c>
+      <c r="B460">
+        <v>2.182057261840934E-4</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A461" s="1">
+        <v>39234</v>
+      </c>
+      <c r="B461">
+        <v>-6.7566905072982228E-2</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A462" s="1">
+        <v>39264</v>
+      </c>
+      <c r="B462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A463" s="1">
+        <v>39295</v>
+      </c>
+      <c r="B463">
+        <v>4.2785810752687677E-2</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A464" s="1">
+        <v>39326</v>
+      </c>
+      <c r="B464">
+        <v>-0.54003090924659203</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A465" s="1">
+        <v>39356</v>
+      </c>
+      <c r="B465">
+        <v>-0.26052116788251312</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A466" s="1">
+        <v>39387</v>
+      </c>
+      <c r="B466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A467" s="1">
+        <v>39417</v>
+      </c>
+      <c r="B467">
+        <v>-7.9949104855756015E-2</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A468" s="1">
+        <v>39448</v>
+      </c>
+      <c r="B468">
+        <v>-0.45557856454899853</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A469" s="1">
+        <v>39479</v>
+      </c>
+      <c r="B469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A470" s="1">
+        <v>39508</v>
+      </c>
+      <c r="B470">
+        <v>-0.52285445502854111</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A471" s="1">
+        <v>39539</v>
+      </c>
+      <c r="B471">
+        <v>-0.20817870530565386</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A472" s="1">
+        <v>39569</v>
+      </c>
+      <c r="B472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A473" s="1">
+        <v>39600</v>
+      </c>
+      <c r="B473">
+        <v>-0.40929872597956357</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A474" s="1">
+        <v>39630</v>
+      </c>
+      <c r="B474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A475" s="1">
+        <v>39661</v>
+      </c>
+      <c r="B475">
+        <v>8.5519188576681254E-2</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A476" s="1">
+        <v>39692</v>
+      </c>
+      <c r="B476">
+        <v>-4.5336797874303572E-2</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A477" s="1">
+        <v>39722</v>
+      </c>
+      <c r="B477">
+        <v>3.3236242875587019E-2</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A478" s="1">
+        <v>39753</v>
+      </c>
+      <c r="B478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A479" s="1">
+        <v>39783</v>
+      </c>
+      <c r="B479">
+        <v>-0.13623363622046003</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A480" s="1">
+        <v>39814</v>
+      </c>
+      <c r="B480">
+        <v>0.28022422916748363</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A481" s="1">
+        <v>39845</v>
+      </c>
+      <c r="B481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A482" s="1">
+        <v>39873</v>
+      </c>
+      <c r="B482">
+        <v>0.54756670880571878</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A483" s="1">
+        <v>39904</v>
+      </c>
+      <c r="B483">
+        <v>4.3308803775541839E-2</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A484" s="1">
+        <v>39934</v>
+      </c>
+      <c r="B484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A485" s="1">
+        <v>39965</v>
+      </c>
+      <c r="B485">
+        <v>7.1310410798964538E-2</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A486" s="1">
+        <v>39995</v>
+      </c>
+      <c r="B486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A487" s="1">
+        <v>40026</v>
+      </c>
+      <c r="B487">
+        <v>0.10644715002261254</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A488" s="1">
+        <v>40057</v>
+      </c>
+      <c r="B488">
+        <v>-0.15364602547705558</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A489" s="1">
+        <v>40087</v>
+      </c>
+      <c r="B489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A490" s="1">
+        <v>40118</v>
+      </c>
+      <c r="B490">
+        <v>3.9008982485992431E-2</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A491" s="1">
+        <v>40148</v>
+      </c>
+      <c r="B491">
+        <v>-4.690953477731289E-2</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A492" s="1">
+        <v>40179</v>
+      </c>
+      <c r="B492">
+        <v>7.3558241476829669E-2</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A493" s="1">
+        <v>40210</v>
+      </c>
+      <c r="B493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A494" s="1">
+        <v>40238</v>
+      </c>
+      <c r="B494">
+        <v>0.14530757130458105</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A495" s="1">
+        <v>40269</v>
+      </c>
+      <c r="B495">
+        <v>4.4626615366468114E-2</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A496" s="1">
+        <v>40299</v>
+      </c>
+      <c r="B496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A497" s="1">
+        <v>40330</v>
+      </c>
+      <c r="B497">
+        <v>9.2262614168595575E-2</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A498" s="1">
+        <v>40360</v>
+      </c>
+      <c r="B498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A499" s="1">
+        <v>40391</v>
+      </c>
+      <c r="B499">
+        <v>0.12892401700454192</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A500" s="1">
+        <v>40422</v>
+      </c>
+      <c r="B500">
+        <v>0.17684707761008384</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A501" s="1">
+        <v>40452</v>
+      </c>
+      <c r="B501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A502" s="1">
+        <v>40483</v>
+      </c>
+      <c r="B502">
+        <v>1.0222325435488991E-2</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A503" s="1">
+        <v>40513</v>
+      </c>
+      <c r="B503">
+        <v>-9.1272793612663425E-2</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A504" s="1">
+        <v>40544</v>
+      </c>
+      <c r="B504">
+        <v>-3.3478213352453393E-4</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A505" s="1">
+        <v>40575</v>
+      </c>
+      <c r="B505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A506" s="1">
+        <v>40603</v>
+      </c>
+      <c r="B506">
+        <v>3.2939377200155807E-2</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A507" s="1">
+        <v>40634</v>
+      </c>
+      <c r="B507">
+        <v>0.12594857342999832</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A508" s="1">
+        <v>40664</v>
+      </c>
+      <c r="B508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A509" s="1">
+        <v>40695</v>
+      </c>
+      <c r="B509">
+        <v>0.17079333448688999</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A510" s="1">
+        <v>40725</v>
+      </c>
+      <c r="B510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A511" s="1">
+        <v>40756</v>
+      </c>
+      <c r="B511">
+        <v>0.20042307128433634</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A512" s="1">
+        <v>40787</v>
+      </c>
+      <c r="B512">
+        <v>0.12243926736742888</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A513" s="1">
+        <v>40817</v>
+      </c>
+      <c r="B513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A514" s="1">
+        <v>40848</v>
+      </c>
+      <c r="B514">
+        <v>-6.6902399148938543E-2</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A515" s="1">
+        <v>40878</v>
+      </c>
+      <c r="B515">
+        <v>-0.13010204780579368</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A516" s="1">
+        <v>40909</v>
+      </c>
+      <c r="B516">
+        <v>0.12152745531156804</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A517" s="1">
+        <v>40940</v>
+      </c>
+      <c r="B517">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A518" s="1">
+        <v>40969</v>
+      </c>
+      <c r="B518">
+        <v>-1.5277114953290859E-2</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A519" s="1">
+        <v>41000</v>
+      </c>
+      <c r="B519">
+        <v>-1.9033319639089403E-2</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A520" s="1">
+        <v>41030</v>
+      </c>
+      <c r="B520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A521" s="1">
+        <v>41061</v>
+      </c>
+      <c r="B521">
+        <v>0.1284524550543277</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A522" s="1">
+        <v>41091</v>
+      </c>
+      <c r="B522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A523" s="1">
+        <v>41122</v>
+      </c>
+      <c r="B523">
+        <v>0.15691624279286973</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A524" s="1">
+        <v>41153</v>
+      </c>
+      <c r="B524">
+        <v>5.060113499018238E-2</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A525" s="1">
+        <v>41183</v>
+      </c>
+      <c r="B525">
+        <v>-4.7109958088981246E-2</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A526" s="1">
+        <v>41214</v>
+      </c>
+      <c r="B526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A527" s="1">
+        <v>41244</v>
+      </c>
+      <c r="B527">
+        <v>0.12608548425558719</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A528" s="1">
+        <v>41275</v>
+      </c>
+      <c r="B528">
+        <v>-6.3102611952402493E-2</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A529" s="1">
+        <v>41306</v>
+      </c>
+      <c r="B529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A530" s="1">
+        <v>41334</v>
+      </c>
+      <c r="B530">
+        <v>5.5541508435375885E-2</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A531" s="1">
+        <v>41365</v>
+      </c>
+      <c r="B531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A532" s="1">
+        <v>41395</v>
+      </c>
+      <c r="B532">
+        <v>4.8941329578167977E-2</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A533" s="1">
+        <v>41426</v>
+      </c>
+      <c r="B533">
+        <v>-3.3450282907336051E-2</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A534" s="1">
+        <v>41456</v>
+      </c>
+      <c r="B534">
+        <v>8.265497674460992E-2</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A535" s="1">
+        <v>41487</v>
+      </c>
+      <c r="B535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A536" s="1">
+        <v>41518</v>
+      </c>
+      <c r="B536">
+        <v>-5.354321594616767E-2</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A537" s="1">
+        <v>41548</v>
+      </c>
+      <c r="B537">
+        <v>1.4363043832176408E-2</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A538" s="1">
+        <v>41579</v>
+      </c>
+      <c r="B538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A539" s="1">
+        <v>41609</v>
+      </c>
+      <c r="B539">
+        <v>-2.1965981096166626E-2</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A540" s="1">
+        <v>41640</v>
+      </c>
+      <c r="B540">
+        <v>-8.1097823669544364E-2</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A541" s="1">
+        <v>41671</v>
+      </c>
+      <c r="B541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A542" s="1">
+        <v>41699</v>
+      </c>
+      <c r="B542">
+        <v>7.1752896999453114E-2</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A543" s="1">
+        <v>41730</v>
+      </c>
+      <c r="B543">
+        <v>-5.2213994821717812E-2</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A544" s="1">
+        <v>41760</v>
+      </c>
+      <c r="B544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A545" s="1">
+        <v>41791</v>
+      </c>
+      <c r="B545">
+        <v>-6.8209601389456032E-2</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A546" s="1">
+        <v>41821</v>
+      </c>
+      <c r="B546">
+        <v>-8.6588174541571597E-2</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A547" s="1">
+        <v>41852</v>
+      </c>
+      <c r="B547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A548" s="1">
+        <v>41883</v>
+      </c>
+      <c r="B548">
+        <v>-1.8914188895364482E-2</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A549" s="1">
+        <v>41913</v>
+      </c>
+      <c r="B549">
+        <v>-2.572623748522581E-2</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A550" s="1">
+        <v>41944</v>
+      </c>
+      <c r="B550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A551" s="1">
+        <v>41974</v>
+      </c>
+      <c r="B551">
+        <v>-5.2188684262572645E-3</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A552" s="1">
+        <v>42005</v>
+      </c>
+      <c r="B552">
+        <v>-9.2563875215391819E-2</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A553" s="1">
+        <v>42036</v>
+      </c>
+      <c r="B553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A554" s="1">
+        <v>42064</v>
+      </c>
+      <c r="B554">
+        <v>7.8641508069745861E-2</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A555" s="1">
+        <v>42095</v>
+      </c>
+      <c r="B555">
+        <v>5.6193177279207841E-2</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A556" s="1">
+        <v>42125</v>
+      </c>
+      <c r="B556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A557" s="1">
+        <v>42156</v>
+      </c>
+      <c r="B557">
+        <v>5.3528292349456996E-2</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A558" s="1">
+        <v>42186</v>
+      </c>
+      <c r="B558">
+        <v>-2.7873582428760323E-2</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A559" s="1">
+        <v>42217</v>
+      </c>
+      <c r="B559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A560" s="1">
+        <v>42248</v>
+      </c>
+      <c r="B560">
+        <v>-9.5153377730114327E-2</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A561" s="1">
+        <v>42278</v>
+      </c>
+      <c r="B561">
+        <v>-4.6205378886410235E-2</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A562" s="1">
+        <v>42309</v>
+      </c>
+      <c r="B562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A563" s="1">
+        <v>42339</v>
+      </c>
+      <c r="B563">
+        <v>0.22252967795208009</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A564" s="1">
+        <v>42370</v>
+      </c>
+      <c r="B564">
+        <v>5.2465178062952736E-3</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A565" s="1">
+        <v>42401</v>
+      </c>
+      <c r="B565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A566" s="1">
+        <v>42430</v>
+      </c>
+      <c r="B566">
+        <v>-6.7603781024344778E-2</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A567" s="1">
+        <v>42461</v>
+      </c>
+      <c r="B567">
+        <v>-2.8172414142573752E-3</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A568" s="1">
+        <v>42491</v>
+      </c>
+      <c r="B568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A569" s="1">
+        <v>42522</v>
+      </c>
+      <c r="B569">
+        <v>-1.4473994359596896E-2</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A570" s="1">
+        <v>42552</v>
+      </c>
+      <c r="B570">
+        <v>-4.8117511373493627E-2</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A571" s="1">
+        <v>42583</v>
+      </c>
+      <c r="B571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A572" s="1">
+        <v>42614</v>
+      </c>
+      <c r="B572">
+        <v>-0.22003087905605068</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A573" s="1">
+        <v>42644</v>
+      </c>
+      <c r="B573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A574" s="1">
+        <v>42675</v>
+      </c>
+      <c r="B574">
+        <v>-1.4594438708913441E-2</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A575" s="1">
+        <v>42705</v>
+      </c>
+      <c r="B575">
+        <v>0.22779709149783045</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A576" s="1">
+        <v>42736</v>
+      </c>
+      <c r="B576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A577" s="1">
+        <v>42767</v>
+      </c>
+      <c r="B577">
+        <v>-2.0907300612589667E-2</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A578" s="1">
+        <v>42795</v>
+      </c>
+      <c r="B578">
+        <v>0.29064721365841206</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A579" s="1">
+        <v>42826</v>
+      </c>
+      <c r="B579">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A580" s="1">
+        <v>42856</v>
+      </c>
+      <c r="B580">
+        <v>-0.10808790450266338</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A581" s="1">
+        <v>42887</v>
+      </c>
+      <c r="B581">
+        <v>0.13091906144767168</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A582" s="1">
+        <v>42917</v>
+      </c>
+      <c r="B582">
+        <v>-1.9979353350151764E-2</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A583" s="1">
+        <v>42948</v>
+      </c>
+      <c r="B583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A584" s="1">
+        <v>42979</v>
+      </c>
+      <c r="B584">
+        <v>-0.13626285726031351</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A585" s="1">
+        <v>43009</v>
+      </c>
+      <c r="B585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A586" s="1">
+        <v>43040</v>
+      </c>
+      <c r="B586">
+        <v>-8.4777374734999911E-2</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A587" s="1">
+        <v>43070</v>
+      </c>
+      <c r="B587">
+        <v>0.24656351175093161</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A588" s="1">
+        <v>43101</v>
+      </c>
+      <c r="B588">
+        <v>-0.16919220804041041</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A589" s="1">
+        <v>43132</v>
+      </c>
+      <c r="B589">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A590" s="1">
+        <v>43160</v>
+      </c>
+      <c r="B590">
+        <v>0.24745192861462703</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A591" s="1">
+        <v>43191</v>
+      </c>
+      <c r="B591">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A592" s="1">
+        <v>43221</v>
+      </c>
+      <c r="B592">
+        <v>-7.0486831422425927E-2</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A593" s="1">
+        <v>43252</v>
+      </c>
+      <c r="B593">
+        <v>0.12596552180000095</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A594" s="1">
+        <v>43282</v>
+      </c>
+      <c r="B594">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A595" s="1">
+        <v>43313</v>
+      </c>
+      <c r="B595">
+        <v>-0.11147339158951625</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A596" s="1">
+        <v>43344</v>
+      </c>
+      <c r="B596">
+        <v>4.779033555916351E-2</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A597" s="1">
+        <v>43374</v>
+      </c>
+      <c r="B597">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A598" s="1">
+        <v>43405</v>
+      </c>
+      <c r="B598">
+        <v>-0.11799025821931636</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A599" s="1">
+        <v>43435</v>
+      </c>
+      <c r="B599">
+        <v>0.18490253406959362</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A600" s="1">
+        <v>43466</v>
+      </c>
+      <c r="B600">
+        <v>-4.5917990320523447E-2</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A601" s="1">
+        <v>43497</v>
+      </c>
+      <c r="B601">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A602" s="1">
+        <v>43525</v>
+      </c>
+      <c r="B602">
+        <v>0.10595946479377341</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A603" s="1">
+        <v>43556</v>
+      </c>
+      <c r="B603">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A604" s="1">
+        <v>43586</v>
+      </c>
+      <c r="B604">
+        <v>2.5501273413135673E-2</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A605" s="1">
+        <v>43617</v>
+      </c>
+      <c r="B605">
+        <v>3.2688180642502951E-2</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A606" s="1">
+        <v>43647</v>
+      </c>
+      <c r="B606">
+        <v>-0.3156112599300957</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A607" s="1">
+        <v>43678</v>
+      </c>
+      <c r="B607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A608" s="1">
+        <v>43709</v>
+      </c>
+      <c r="B608">
+        <v>-0.30388865391716219</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A609" s="1">
+        <v>43739</v>
+      </c>
+      <c r="B609">
+        <v>-0.28072507153921672</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A610" s="1">
+        <v>43770</v>
+      </c>
+      <c r="B610">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A611" s="1">
+        <v>43800</v>
+      </c>
+      <c r="B611">
+        <v>-2.169308853025298E-2</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A612" s="1">
+        <v>43831</v>
+      </c>
+      <c r="B612">
+        <v>-6.9431788129300773E-2</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A613" s="1">
+        <v>43862</v>
+      </c>
+      <c r="B613">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A614" s="1">
+        <v>43891</v>
+      </c>
+      <c r="B614">
+        <v>-0.91246967420715508</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A615" s="1">
+        <v>43922</v>
+      </c>
+      <c r="B615">
+        <v>3.7826475824082615</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A616" s="1">
+        <v>43952</v>
+      </c>
+      <c r="B616">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A617" s="1">
+        <v>43983</v>
+      </c>
+      <c r="B617">
+        <v>0.85482422116270573</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A618" s="1">
+        <v>44013</v>
+      </c>
+      <c r="B618">
+        <v>0.89262133795220266</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A619" s="1">
+        <v>44044</v>
+      </c>
+      <c r="B619">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A620" s="1">
+        <v>44075</v>
+      </c>
+      <c r="B620">
+        <v>-1.4297274233381045</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A621" s="1">
+        <v>44105</v>
+      </c>
+      <c r="B621">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A622" s="1">
+        <v>44136</v>
+      </c>
+      <c r="B622">
+        <v>-0.25750465399494593</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A623" s="1">
+        <v>44166</v>
+      </c>
+      <c r="B623">
         <v>-0.39679045397726492</v>
       </c>
     </row>
